--- a/www/flightdata/xlsx/eoss-321.xlsx
+++ b/www/flightdata/xlsx/eoss-321.xlsx
@@ -4218,7 +4218,7 @@
         <v>28943.5</v>
       </c>
       <c r="I2">
-        <v>794</v>
+        <v>566</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
